--- a/Data/EXCEL/Transfer/salemon/202412/2311-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/2311-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BE54E89-68F4-47FC-AC72-AE4B4F4BDB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E87F3CF1-83F7-4FE0-A1DF-742B6818F735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{9A48BC91-CD87-4598-B2E0-569BC57708F4}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{3E3BA9C2-0355-4E53-9DE7-70003F3201FA}"/>
   </bookViews>
   <sheets>
     <sheet name="2311-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1264,23 +1264,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A3D61D-282C-43D1-BC99-224313EE143B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C2BF8C-4F42-4F5F-BC3F-68E0A339716E}">
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="7" width="14.54296875" customWidth="1"/>
-    <col min="8" max="8" width="15.26953125" customWidth="1"/>
-    <col min="9" max="10" width="14.54296875" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" customWidth="1"/>
-    <col min="12" max="12" width="14.54296875" customWidth="1"/>
-    <col min="13" max="13" width="15.26953125" customWidth="1"/>
-    <col min="14" max="15" width="14.54296875" customWidth="1"/>
-    <col min="16" max="16" width="15.26953125" customWidth="1"/>
-    <col min="17" max="17" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="7" width="9.625" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="9.625" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="9.625" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="15" width="9.625" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +1307,7 @@
       <c r="P1" s="22"/>
       <c r="Q1" s="23"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="19"/>
       <c r="B2" s="18" t="s">
         <v>4</v>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Q2" s="23"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="19"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -1389,7 +1389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="20"/>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -1428,7 +1428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45292</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>-2.87</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>45261</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>-16.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45231</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>-17.100000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>45200</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>-16.899999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45170</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>45139</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>-17.2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45108</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>-17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>45078</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45047</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>-16.3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>45017</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>-15.7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>44986</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>-13.2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>44958</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>44927</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>44896</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>44866</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>44835</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>44805</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>44774</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>44743</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>44713</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>44682</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>44652</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>44621</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>44593</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>44562</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>44531</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>44501</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>44470</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>44440</v>
       </c>
